--- a/improvement/realestate/plan-01.xlsx
+++ b/improvement/realestate/plan-01.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>来店を前提とした契約フローをやめ、印紙代と郵送の往復をまとめてなくす</t>
+          <t>来店を前提とした契約フローをやめ、郵送の往復と締結待ちの日数をまとめてなくす</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>約5ヶ月</t>
+          <t>約6ヶ月</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>電子契約システムとIT重説の環境を一体で導入し、契約手続きを完全非対面で完結させる。契約事務の月27時間を7時間へ減らし、締結までの日数を9日から2日へ短縮する。あわせて賃貸借契約書の印紙税負担をなくす。</t>
+          <t>電子契約システムとIT重説の環境を一体で導入し、契約手続きを完全非対面で完結させる。契約事務の月27時間を7時間へ減らし、締結までの日数を9日から2日へ短縮する。</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>4.6万円/月</t>
+          <t>3.6万円/月</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>削減される月20時間を営業・事務人件費1,800円/時で換算した月3.6万円に、賃貸借契約書の印紙代（月22件想定）の削減分を月1.0万円と見積もり合算。成約先送りの解消による増収は計上していない。</t>
+          <t>削減される月20時間を営業・事務人件費1,800円/時で換算して月3.6万円。印紙代は、建物の賃貸借契約書がもともと印紙税の課税対象でないため削減効果に計上しない。成約先送りの解消による増収も計上していない。</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>電子契約による賃貸借契約書は印紙税の課税文書に該当しないとされ、印紙代の負担がなくなる（国税庁 見解）</t>
+          <t>建物の賃貸借契約書は書面で作成しても印紙税の課税対象にならない（国税庁タックスアンサーNo.7106）。土地の賃貸借契約書や売買契約書など課税文書にあたるものは、電子契約で締結すれば印紙が不要とされる</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>紙の契約も選択できる二本立てとし、電子契約の利点（印紙代不要・郵送不要）を案内資料で説明する</t>
+          <t>紙の契約も選択できる二本立てとし、電子契約の利点（郵送不要・締結が早い）を案内資料で説明する</t>
         </is>
       </c>
     </row>
